--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121669968</v>
+        <v>121669986</v>
       </c>
       <c r="B4" t="n">
-        <v>96740</v>
+        <v>94408</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322954</v>
+        <v>322959</v>
       </c>
       <c r="R4" t="n">
-        <v>6379144</v>
+        <v>6379182</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121669999</v>
+        <v>121669968</v>
       </c>
       <c r="B5" t="n">
-        <v>94885</v>
+        <v>96740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322977</v>
+        <v>322954</v>
       </c>
       <c r="R5" t="n">
-        <v>6379193</v>
+        <v>6379144</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121670024</v>
+        <v>121669999</v>
       </c>
       <c r="B6" t="n">
-        <v>96740</v>
+        <v>94885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322960</v>
+        <v>322977</v>
       </c>
       <c r="R6" t="n">
-        <v>6379182</v>
+        <v>6379193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121669986</v>
+        <v>121670024</v>
       </c>
       <c r="B7" t="n">
-        <v>94408</v>
+        <v>96740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322959</v>
+        <v>322960</v>
       </c>
       <c r="R7" t="n">
         <v>6379182</v>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121670006</v>
+        <v>121670024</v>
       </c>
       <c r="B3" t="n">
-        <v>5167</v>
+        <v>96740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102185</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322980</v>
+        <v>322960</v>
       </c>
       <c r="R3" t="n">
-        <v>6379272</v>
+        <v>6379182</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121669986</v>
+        <v>121669999</v>
       </c>
       <c r="B4" t="n">
-        <v>94408</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322959</v>
+        <v>322977</v>
       </c>
       <c r="R4" t="n">
-        <v>6379182</v>
+        <v>6379193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121669999</v>
+        <v>121670006</v>
       </c>
       <c r="B6" t="n">
-        <v>94885</v>
+        <v>5167</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>102185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322977</v>
+        <v>322980</v>
       </c>
       <c r="R6" t="n">
-        <v>6379193</v>
+        <v>6379272</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121670024</v>
+        <v>121669986</v>
       </c>
       <c r="B7" t="n">
-        <v>96740</v>
+        <v>94408</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322960</v>
+        <v>322959</v>
       </c>
       <c r="R7" t="n">
         <v>6379182</v>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121670024</v>
+        <v>121669999</v>
       </c>
       <c r="B3" t="n">
-        <v>96740</v>
+        <v>94885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322960</v>
+        <v>322977</v>
       </c>
       <c r="R3" t="n">
-        <v>6379182</v>
+        <v>6379193</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121669999</v>
+        <v>121669968</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>96740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322977</v>
+        <v>322954</v>
       </c>
       <c r="R4" t="n">
-        <v>6379193</v>
+        <v>6379144</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121669968</v>
+        <v>121670006</v>
       </c>
       <c r="B5" t="n">
-        <v>96740</v>
+        <v>5167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>102185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322954</v>
+        <v>322980</v>
       </c>
       <c r="R5" t="n">
-        <v>6379144</v>
+        <v>6379272</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121670006</v>
+        <v>121670024</v>
       </c>
       <c r="B6" t="n">
-        <v>5167</v>
+        <v>96740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102185</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322980</v>
+        <v>322960</v>
       </c>
       <c r="R6" t="n">
-        <v>6379272</v>
+        <v>6379182</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121669999</v>
+        <v>121670024</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>96740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322977</v>
+        <v>322960</v>
       </c>
       <c r="R3" t="n">
-        <v>6379193</v>
+        <v>6379182</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121669968</v>
+        <v>121669999</v>
       </c>
       <c r="B4" t="n">
-        <v>96740</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322954</v>
+        <v>322977</v>
       </c>
       <c r="R4" t="n">
-        <v>6379144</v>
+        <v>6379193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121670006</v>
+        <v>121669986</v>
       </c>
       <c r="B5" t="n">
-        <v>5167</v>
+        <v>94408</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102185</v>
+        <v>2779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322980</v>
+        <v>322959</v>
       </c>
       <c r="R5" t="n">
-        <v>6379272</v>
+        <v>6379182</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121670024</v>
+        <v>121669968</v>
       </c>
       <c r="B6" t="n">
         <v>96740</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322960</v>
+        <v>322954</v>
       </c>
       <c r="R6" t="n">
-        <v>6379182</v>
+        <v>6379144</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121669986</v>
+        <v>121670006</v>
       </c>
       <c r="B7" t="n">
-        <v>94408</v>
+        <v>5167</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>102185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322959</v>
+        <v>322980</v>
       </c>
       <c r="R7" t="n">
-        <v>6379182</v>
+        <v>6379272</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121670024</v>
+        <v>121669999</v>
       </c>
       <c r="B3" t="n">
-        <v>96740</v>
+        <v>94885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322960</v>
+        <v>322977</v>
       </c>
       <c r="R3" t="n">
-        <v>6379182</v>
+        <v>6379193</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121669999</v>
+        <v>121669968</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>96740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322977</v>
+        <v>322954</v>
       </c>
       <c r="R4" t="n">
-        <v>6379193</v>
+        <v>6379144</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121669986</v>
+        <v>121670024</v>
       </c>
       <c r="B5" t="n">
-        <v>94408</v>
+        <v>96740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322959</v>
+        <v>322960</v>
       </c>
       <c r="R5" t="n">
         <v>6379182</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121669968</v>
+        <v>121669986</v>
       </c>
       <c r="B6" t="n">
-        <v>96740</v>
+        <v>94408</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322954</v>
+        <v>322959</v>
       </c>
       <c r="R6" t="n">
-        <v>6379144</v>
+        <v>6379182</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121669999</v>
+        <v>121669968</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>96740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322977</v>
+        <v>322954</v>
       </c>
       <c r="R3" t="n">
-        <v>6379193</v>
+        <v>6379144</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121669968</v>
+        <v>121670024</v>
       </c>
       <c r="B4" t="n">
         <v>96740</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322954</v>
+        <v>322960</v>
       </c>
       <c r="R4" t="n">
-        <v>6379144</v>
+        <v>6379182</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121670024</v>
+        <v>121670006</v>
       </c>
       <c r="B5" t="n">
-        <v>96740</v>
+        <v>5167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>102185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322960</v>
+        <v>322980</v>
       </c>
       <c r="R5" t="n">
-        <v>6379182</v>
+        <v>6379272</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121669986</v>
+        <v>121669999</v>
       </c>
       <c r="B6" t="n">
-        <v>94408</v>
+        <v>94885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2779</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322959</v>
+        <v>322977</v>
       </c>
       <c r="R6" t="n">
-        <v>6379182</v>
+        <v>6379193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121670006</v>
+        <v>121669986</v>
       </c>
       <c r="B7" t="n">
-        <v>5167</v>
+        <v>94408</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102185</v>
+        <v>2779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322980</v>
+        <v>322959</v>
       </c>
       <c r="R7" t="n">
-        <v>6379272</v>
+        <v>6379182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121669968</v>
+        <v>121670006</v>
       </c>
       <c r="B3" t="n">
-        <v>96740</v>
+        <v>5167</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>102185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322954</v>
+        <v>322980</v>
       </c>
       <c r="R3" t="n">
-        <v>6379144</v>
+        <v>6379272</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121670024</v>
+        <v>121669968</v>
       </c>
       <c r="B4" t="n">
-        <v>96740</v>
+        <v>96758</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322960</v>
+        <v>322954</v>
       </c>
       <c r="R4" t="n">
-        <v>6379182</v>
+        <v>6379144</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121670006</v>
+        <v>121669986</v>
       </c>
       <c r="B5" t="n">
-        <v>5167</v>
+        <v>94426</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102185</v>
+        <v>2779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322980</v>
+        <v>322959</v>
       </c>
       <c r="R5" t="n">
-        <v>6379272</v>
+        <v>6379182</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1125,7 @@
         <v>121669999</v>
       </c>
       <c r="B6" t="n">
-        <v>94885</v>
+        <v>94903</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121669986</v>
+        <v>121670024</v>
       </c>
       <c r="B7" t="n">
-        <v>94408</v>
+        <v>96758</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322959</v>
+        <v>322960</v>
       </c>
       <c r="R7" t="n">
         <v>6379182</v>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121670006</v>
+        <v>121669986</v>
       </c>
       <c r="B3" t="n">
-        <v>5167</v>
+        <v>94428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102185</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322980</v>
+        <v>322959</v>
       </c>
       <c r="R3" t="n">
-        <v>6379272</v>
+        <v>6379182</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,7 +911,7 @@
         <v>121669968</v>
       </c>
       <c r="B4" t="n">
-        <v>96758</v>
+        <v>96760</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121669986</v>
+        <v>121670024</v>
       </c>
       <c r="B5" t="n">
-        <v>94426</v>
+        <v>96760</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322959</v>
+        <v>322960</v>
       </c>
       <c r="R5" t="n">
         <v>6379182</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121669999</v>
+        <v>121670006</v>
       </c>
       <c r="B6" t="n">
-        <v>94903</v>
+        <v>5167</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>102185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322977</v>
+        <v>322980</v>
       </c>
       <c r="R6" t="n">
-        <v>6379193</v>
+        <v>6379272</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121670024</v>
+        <v>121669999</v>
       </c>
       <c r="B7" t="n">
-        <v>96758</v>
+        <v>94905</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322960</v>
+        <v>322977</v>
       </c>
       <c r="R7" t="n">
-        <v>6379182</v>
+        <v>6379193</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121669986</v>
+        <v>121670024</v>
       </c>
       <c r="B3" t="n">
-        <v>94428</v>
+        <v>96767</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322959</v>
+        <v>322960</v>
       </c>
       <c r="R3" t="n">
         <v>6379182</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121669968</v>
+        <v>121669986</v>
       </c>
       <c r="B4" t="n">
-        <v>96760</v>
+        <v>94435</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322954</v>
+        <v>322959</v>
       </c>
       <c r="R4" t="n">
-        <v>6379144</v>
+        <v>6379182</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121670024</v>
+        <v>121669999</v>
       </c>
       <c r="B5" t="n">
-        <v>96760</v>
+        <v>94912</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322960</v>
+        <v>322977</v>
       </c>
       <c r="R5" t="n">
-        <v>6379182</v>
+        <v>6379193</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121669999</v>
+        <v>121669968</v>
       </c>
       <c r="B7" t="n">
-        <v>94905</v>
+        <v>96767</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322977</v>
+        <v>322954</v>
       </c>
       <c r="R7" t="n">
-        <v>6379193</v>
+        <v>6379144</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121670024</v>
+        <v>121669986</v>
       </c>
       <c r="B3" t="n">
-        <v>96767</v>
+        <v>94444</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322960</v>
+        <v>322959</v>
       </c>
       <c r="R3" t="n">
         <v>6379182</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121669986</v>
+        <v>121670006</v>
       </c>
       <c r="B4" t="n">
-        <v>94435</v>
+        <v>5167</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
+        <v>102185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322959</v>
+        <v>322980</v>
       </c>
       <c r="R4" t="n">
-        <v>6379182</v>
+        <v>6379272</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1018,7 @@
         <v>121669999</v>
       </c>
       <c r="B5" t="n">
-        <v>94912</v>
+        <v>94921</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121670006</v>
+        <v>121670024</v>
       </c>
       <c r="B6" t="n">
-        <v>5167</v>
+        <v>96776</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102185</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322980</v>
+        <v>322960</v>
       </c>
       <c r="R6" t="n">
-        <v>6379272</v>
+        <v>6379182</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1232,7 @@
         <v>121669968</v>
       </c>
       <c r="B7" t="n">
-        <v>96767</v>
+        <v>96776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2703</v>
+        <v>121669999</v>
       </c>
       <c r="B2" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100084</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandsjöbacka NR, Hl</t>
+          <t>Sandsjöbacka (Naturreservat), Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323007.1327707081</v>
+        <v>322977</v>
       </c>
       <c r="R2" t="n">
-        <v>6379280.256675788</v>
+        <v>6379193</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-09-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Otillgängligt ravinområde i bergsslänt åt öster med kraftledning och ymnigt inslag av ädellöv och täta busksnår. Ofta enbuskar och hassel, särskilt i södra delen. Området granskades under pågående hasselmusinventering i Kungsbacka kommun.</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,31 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Viktor Bolin</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Paulina Wietrzyk-Pelka</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Paulina Wietrzyk-Pelka, Viktor Bolin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121669986</v>
+        <v>121669968</v>
       </c>
       <c r="B3" t="n">
-        <v>94444</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322959</v>
+        <v>322954</v>
       </c>
       <c r="R3" t="n">
-        <v>6379182</v>
+        <v>6379144</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121670006</v>
+        <v>121670024</v>
       </c>
       <c r="B4" t="n">
-        <v>5167</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102185</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322980</v>
+        <v>322960</v>
       </c>
       <c r="R4" t="n">
-        <v>6379272</v>
+        <v>6379182</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121669999</v>
+        <v>121669986</v>
       </c>
       <c r="B5" t="n">
-        <v>94921</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322977</v>
+        <v>322959</v>
       </c>
       <c r="R5" t="n">
-        <v>6379193</v>
+        <v>6379182</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121670024</v>
+        <v>121669844</v>
       </c>
       <c r="B6" t="n">
-        <v>96776</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322960</v>
+        <v>322955</v>
       </c>
       <c r="R6" t="n">
-        <v>6379182</v>
+        <v>6379118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1167,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Viktor Bolin</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1222,22 +1178,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Paulina Wietrzyk-Pelka, Viktor Bolin</t>
+          <t>Paulina Wietrzyk-Pelka, Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121669968</v>
+        <v>2703</v>
       </c>
       <c r="B7" t="n">
-        <v>96776</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,34 +1196,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>100084</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandsjöbacka (Naturreservat), Hl</t>
+          <t>Sandsjöbacka NR, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322954</v>
+        <v>323007</v>
       </c>
       <c r="R7" t="n">
-        <v>6379144</v>
+        <v>6379280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,12 +1259,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2008-09-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2008-09-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Otillgängligt ravinområde i bergsslänt åt öster med kraftledning och ymnigt inslag av ädellöv och täta busksnår. Ofta enbuskar och hassel, särskilt i södra delen. Området granskades under pågående hasselmusinventering i Kungsbacka kommun.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,24 +1280,465 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Viktor Bolin</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>56701</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sandsjöbacka NR södra lokalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>323017</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6379196</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tölö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2008-08-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2008-09-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kraftledningsavsnitt i den södra delen av optimalt utseende. Utsökt fina kratt av hassel och ek. Samma y-koord - troligen samma hane. Hanbo i ek. Hotas av röjning under den sårbara yngelperioden.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Viveka Strand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>56702</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sandsjöbacka NR södra lokalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>323017</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6379194</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tölö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2008-08-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2008-09-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kraftledningsavsnitt i den södra delen av optimalt utseende. Utsökt fina kratt av hassel och ek. Samma y-koord - troligen samma hane. Hanbo i ek. Hotas av röjning under den sårbara yngelperioden.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Viveka Strand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121670006</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5173</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Myskbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Aromia moschata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sandsjöbacka (Naturreservat), Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>322980</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6379272</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tölö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Viktor Bolin</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Paulina Wietrzyk-Pelka</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Paulina Wietrzyk-Pelka, Viktor Bolin</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121669917</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sandsjöbacka (Naturreservat), Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>322955</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6379107</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tölö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Paulina Wietrzyk-Pelka</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Paulina Wietrzyk-Pelka, Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63965-2021 artfynd.xlsx
+++ b/artfynd/A 63965-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669999</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669968</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121670024</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669986</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669844</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2703</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56701</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56702</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121670006</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,8 +1789,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669917</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>